--- a/outputs/04_phase_01_correlations_numerical.xlsx
+++ b/outputs/04_phase_01_correlations_numerical.xlsx
@@ -4084,7 +4084,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>notebooks/phase_01_market_rent/04_numerical_correlations.ipynb on 2026-10-22</t>
+          <t>notebooks/phase_01_market_rent/04_numerical_correlations.ipynb on 2026-10-24</t>
         </is>
       </c>
     </row>
